--- a/4_極性指数平均算出/output.xlsx
+++ b/4_極性指数平均算出/output.xlsx
@@ -1,22 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hikar\Desktop\exel分析\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hikar\Desktop\2025_radio\4_極性指数平均算出\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{259147AF-652F-41C3-8A07-F0AF070DD9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A69F9-A47F-4C61-B659-E887E7394400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="15800" xr2:uid="{E672F5F0-36B5-4686-9DB7-70A623391450}"/>
+    <workbookView xWindow="0" yWindow="367" windowWidth="26300" windowHeight="15799" xr2:uid="{E672F5F0-36B5-4686-9DB7-70A623391450}"/>
   </bookViews>
   <sheets>
     <sheet name="output" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,6 +745,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US" sz="1200"/>
+              <a:t>年表の各メディアの事例が持つ印象の各年の平均の推移</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -748,8 +808,19 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>output!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>radio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="12700" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -760,314 +831,626 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>output!$B$3:$B$103</c:f>
+              <c:f>output!$A$2:$A$102</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
+                  <c:v>1923</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1924</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1925</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>output!$B$2:$B$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="101"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>-0.38905920100000002</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-0.38078603300000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-0.367794014</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>-0.43469751400000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>-0.41295840299999997</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>-0.25110952600000003</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>-0.321371872</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>-0.44817083499999999</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>-0.43505021300000002</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>-0.40578381200000002</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>-0.41979019200000001</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>-0.44598187099999997</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>-0.39794013700000003</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>-0.41113577800000001</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>-0.37664842599999998</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>-0.38144841299999999</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>-0.40409305099999998</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>-0.39127214599999999</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>-0.41544682999999999</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>-0.405924538</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>-0.445464586</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>-0.40905995899999997</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>-0.43157516899999998</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>-0.42754271700000002</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>-0.409683725</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>-0.42090827600000003</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>-0.41234499499999999</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>-0.392252184</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>-0.37787685900000001</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>-0.40319289699999999</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>-0.41142029800000002</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>-0.41403933100000001</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>-0.41628045699999999</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>-0.390346684</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>-0.40215126800000001</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>-0.41620091300000001</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>-0.40630872200000001</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>-0.38210140300000001</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>-0.40883208799999998</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>-0.43665158399999998</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>-0.396840095</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>-0.40574149100000001</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>-0.37074832099999999</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>-0.403897057</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>-0.41522060500000002</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>-0.42189231599999999</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>-0.45723398900000001</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>-0.41800294300000002</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>-0.38137493300000003</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>-0.42900649400000002</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>-0.40826187200000003</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>-0.422510304</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>-0.42567411399999999</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>-0.41255373899999997</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>-0.36857918299999998</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>-0.42001375499999999</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>-0.419397888</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>-0.36690592399999999</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>-0.40298641200000002</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>-0.39332741900000001</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>-0.41263676399999999</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>-0.39303622599999999</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>-0.37649437899999999</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>-0.40409363700000001</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>-0.35634058200000002</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>-0.39197300299999999</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>-0.37791977700000001</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>-0.41871988199999999</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>-0.38284823899999998</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>-0.38938611499999998</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>-0.392120195</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>-0.37975766799999999</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>-0.38591098000000001</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>-0.401051292</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>-0.36191617100000001</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>-0.35962633900000002</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>-0.406536499</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>-0.35094976500000002</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>-0.37826375099999998</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>-0.38362768800000002</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>-0.36822170100000001</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>-0.339554737</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>-0.372060275</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>-0.35977932499999998</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>-0.35835653200000001</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>-0.34991079899999999</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>-0.352474536</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>-0.34557175299999998</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>-0.338179436</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>-0.31774959200000003</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>-0.33978283100000001</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>-0.31166188900000003</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>-0.330181059</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>-0.33099806199999998</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>-0.33555506499999999</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>-0.322665492</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>-0.34007211599999998</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>-0.36434873400000001</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>-0.38641671300000002</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>-0.37252254099999998</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>-0.33999201000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1082,8 +1465,19 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>output!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>tv</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="12700" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1094,314 +1488,623 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>output!$C$3:$C$103</c:f>
+              <c:f>output!$A$2:$A$102</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
+                  <c:v>1923</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1924</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1925</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>output!$C$2:$C$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="101"/>
+                <c:pt idx="1">
                   <c:v>-0.17502534</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-0.44389171100000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-0.41851084</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>-0.45481665500000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>-0.54019225299999996</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>-0.49332863799999999</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>-0.44705257999999998</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>-0.44623792800000001</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>-0.44301938800000001</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>-0.37833264500000002</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>-0.43513729600000001</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>-0.50060275700000001</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>-0.44503641599999999</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>-0.48901847399999998</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>-0.50796086900000004</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>-0.47632565199999999</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>-0.46445451199999999</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>-0.46682339900000003</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>-0.54103926599999996</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>-0.47057261700000003</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>-0.49765194099999999</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>-0.39371035100000001</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>-0.44974711000000001</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>-0.44432500200000002</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>-0.441643167</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>-0.46941286300000001</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>-0.43393178999999998</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>-0.43502898400000001</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>-0.44820500499999999</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>-0.45908634700000001</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>-0.42616231500000001</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>-0.43784094299999998</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>-0.46313061700000002</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>-0.43446499700000002</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>-0.42794692099999998</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>-0.43272784800000003</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>-0.433449853</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>-0.41795795800000002</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>-0.42845129100000001</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>-0.41425056799999999</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>-0.45206433299999998</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>-0.43638289099999999</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>-0.426855182</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>-0.41092315600000001</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>-0.41026232299999998</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>-0.41322821900000001</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>-0.43029531999999998</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>-0.41595207099999998</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>-0.415064985</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>-0.41171822000000002</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>-0.42152361700000002</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>-0.41361971600000003</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>-0.387958672</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>-0.41034416400000001</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>-0.41230830200000002</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>-0.43272278400000003</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>-0.42046722399999997</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>-0.43842012000000002</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>-0.419277603</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>-0.42963205399999999</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>-0.41327989300000001</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>-0.376207821</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>-0.40672583600000001</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>-0.43402195399999999</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>-0.38594012300000002</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>-0.37599682200000001</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>-0.40463248099999999</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>-0.38593338399999999</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>-0.39792396499999999</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>-0.38671038099999999</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>-0.407792706</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>-0.40401663300000001</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>-0.419907523</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>-0.39662051500000001</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>-0.39077959099999998</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>-0.411385047</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>-0.38907209500000001</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>-0.37176082300000002</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>-0.359719972</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>-0.35513045700000001</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>-0.36181258199999999</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>-0.35823408299999998</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>-0.345225487</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>-0.33509126900000002</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>-0.35642174199999999</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>-0.34214165499999999</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>-0.353350312</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>-0.34337787400000003</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>-0.34047141199999997</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>-0.33757659899999998</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>-0.335658754</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>-0.328807024</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>-0.34527046900000002</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>-0.34146551400000003</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>-0.34403588800000001</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>-0.34553649199999997</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>-0.34235283799999999</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>-0.34129330699999999</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>-0.34270434100000002</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>-0.33402780300000001</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>-0.33893776399999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1416,8 +2119,19 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>output!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>newspaper</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="12700" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
@@ -1428,314 +2142,626 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:val>
+          <c:cat>
             <c:numRef>
-              <c:f>output!$D$3:$D$103</c:f>
+              <c:f>output!$A$2:$A$102</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
+                  <c:v>1923</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1924</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1925</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1929</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1930</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1932</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1933</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1934</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1935</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1937</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1939</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1940</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1941</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1942</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1943</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1945</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1946</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1947</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1948</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1949</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1951</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1952</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1954</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1956</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1957</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1959</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1961</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1963</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1964</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1965</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1966</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1967</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1969</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1970</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1971</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1972</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1973</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1974</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1976</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1977</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1978</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1981</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1983</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1985</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1986</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1987</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1988</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1989</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1990</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1991</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1992</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1994</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1995</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1996</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2004</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2006</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2007</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2008</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2009</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2011</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2012</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2013</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2023</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>output!$D$2:$D$102</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="101"/>
+                <c:pt idx="0">
+                  <c:v>-0.42094521400000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>-0.40992837100000001</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>-0.41867569199999999</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>-0.42645347900000002</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>-0.42302210000000001</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>-0.49652559699999999</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>-0.40041705999999999</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>-0.47855838699999997</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>-0.50772035000000004</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>-0.44965940700000001</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>-0.36369320599999999</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>-0.32575025200000002</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>-0.413179085</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>-0.47368335099999997</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>-0.42279379499999997</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>-0.43620385299999997</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>-0.47327783899999998</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>-0.49648171400000002</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>-0.45593228699999999</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>-0.46381681800000002</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>-0.49741814299999998</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>-0.38456812800000001</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>-0.45499317500000003</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>-0.47217391399999997</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>-0.45433542399999999</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>-0.46965948899999999</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>-0.48076017199999999</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>-0.44196723700000001</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>-0.37831236000000001</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>-0.45115344699999999</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>-0.45796511899999998</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>-0.401893047</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>-0.39704231899999998</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>-0.43591902799999999</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>-0.45627912999999998</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>-0.481186787</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>-0.46158274500000002</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>-0.43640073499999998</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>-0.49589431</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>-0.47890261299999998</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>-0.43470957500000001</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>-0.38400774599999998</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>-0.34760947399999997</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>-0.43230971000000001</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>-0.43643151699999999</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>-0.44729468700000002</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>-0.446671969</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>-0.45393618299999999</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>-0.47685415399999997</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>-0.482305871</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>-0.54364649499999995</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>-0.42071202600000002</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>-0.442304172</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>-0.451605284</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>-0.43049278000000002</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>-0.40023851300000002</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>-0.450117237</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>-0.42399784200000001</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>-0.44684690500000002</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>-0.47206963600000001</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>-0.47014336600000001</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>-0.42974738000000001</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>-0.48445026099999999</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>-0.35097309399999999</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>-0.48123155200000001</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>-0.40006641100000001</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>-0.426006261</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>-0.42889423900000001</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>-0.47288395100000002</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>-0.41260523599999999</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>-0.393411607</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>-0.41048378000000002</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>-0.39488593599999999</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>-0.38306660999999997</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>-0.35679061899999998</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>-0.341300204</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>-0.41505755</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>-0.39787278300000001</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>-0.38044596899999999</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>-0.41224157</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>-0.35718451699999998</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>-0.37315590700000001</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>-0.37091381200000001</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>-0.36271697000000003</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>-0.34984437400000001</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>-0.35342427399999998</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>-0.35561011799999998</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>-0.346931979</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>-0.36628884699999997</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>-0.38747683399999999</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>-0.38961040800000002</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>-0.361713642</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>-0.28708681200000002</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>-0.33304678300000001</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>-0.357711907</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>-0.34660637</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>-0.35995240499999998</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>-0.301845749</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>-0.34140198700000002</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>-0.36201287500000001</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>-0.340697376</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>-0.33415313200000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1766,6 +2792,76 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>年</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1830,6 +2926,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>印象</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -4326,16 +5477,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>224286</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>8625</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>386213</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>42221</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>655607</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>60384</xdr:rowOff>
+      <xdr:colOff>685094</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>23316</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4746,8 +5897,9 @@
       <c r="A2">
         <v>1923</v>
       </c>
-      <c r="B2">
-        <v>-0.25805136899999997</v>
+      <c r="B2" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">B2:D79-0.258051369</f>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>-0.42094521400000001</v>
@@ -7090,6 +8242,7 @@
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>